--- a/medical_surveys_questionnaires/023_hemophilia_treatment_survey--medical_surveys_questionnaires.xlsx
+++ b/medical_surveys_questionnaires/023_hemophilia_treatment_survey--medical_surveys_questionnaires.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1110,8 +1110,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="39" customWidth="1" min="2" max="2"/>
+    <col width="39" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'factor_viii'}</t>
+          <t>factor_viii</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Factor VIII'}</t>
+          <t>Factor VIII</t>
         </is>
       </c>
     </row>
@@ -1156,12 +1156,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1173,12 +1173,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'desmotesplexin'}</t>
+          <t>desmotesplexin</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Desmotesplexin'}</t>
+          <t>Desmotesplexin</t>
         </is>
       </c>
     </row>
@@ -1190,12 +1190,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'other_(please_specify)'}</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Other (please specify)'}</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
@@ -1207,12 +1207,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -1224,12 +1224,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'occasionally'}</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Occasionally'}</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
@@ -1241,12 +1241,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'frequently'}</t>
+          <t>frequently</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Frequently'}</t>
+          <t>Frequently</t>
         </is>
       </c>
     </row>
@@ -1258,12 +1258,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'almost_daily'}</t>
+          <t>almost_daily</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Almost daily'}</t>
+          <t>Almost daily</t>
         </is>
       </c>
     </row>
@@ -1275,12 +1275,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'1_-_very_dissatisfied'}</t>
+          <t>1_-_very_dissatisfied</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': '1 - Very dissatisfied'}</t>
+          <t>1 - Very dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1292,12 +1292,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'2_-_somewhat_dissatisfied'}</t>
+          <t>2_-_somewhat_dissatisfied</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': '2 - Somewhat dissatisfied'}</t>
+          <t>2 - Somewhat dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1309,12 +1309,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'3_-_neutral'}</t>
+          <t>3_-_neutral</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': '3 - Neutral'}</t>
+          <t>3 - Neutral</t>
         </is>
       </c>
     </row>
@@ -1326,12 +1326,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'4_-_somewhat_satisfied'}</t>
+          <t>4_-_somewhat_satisfied</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': '4 - Somewhat satisfied'}</t>
+          <t>4 - Somewhat satisfied</t>
         </is>
       </c>
     </row>
@@ -1343,12 +1343,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'5_-_very_satisfied'}</t>
+          <t>5_-_very_satisfied</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': '5 - Very satisfied'}</t>
+          <t>5 - Very satisfied</t>
         </is>
       </c>
     </row>
@@ -1360,12 +1360,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'reduce_frequency_of_bleeding_episodes'}</t>
+          <t>reduce_frequency_of_bleeding_episodes</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'Reduce frequency of bleeding episodes'}</t>
+          <t>Reduce frequency of bleeding episodes</t>
         </is>
       </c>
     </row>
@@ -1377,12 +1377,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'improve_quality_of_life'}</t>
+          <t>improve_quality_of_life</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'Improve quality of life'}</t>
+          <t>Improve quality of life</t>
         </is>
       </c>
     </row>
@@ -1394,12 +1394,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'manageable_treatment_regimen'}</t>
+          <t>manageable_treatment_regimen</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'Manageable treatment regimen'}</t>
+          <t>Manageable treatment regimen</t>
         </is>
       </c>
     </row>
@@ -1411,12 +1411,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'other_(please_specify)'}</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'Other (please specify)'}</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
@@ -1428,12 +1428,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'hemophilia_a'}</t>
+          <t>hemophilia_a</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 'Hemophilia A'}</t>
+          <t>Hemophilia A</t>
         </is>
       </c>
     </row>
@@ -1445,12 +1445,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_'hemophilia_b'}</t>
+          <t>hemophilia_b</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 'Hemophilia B'}</t>
+          <t>Hemophilia B</t>
         </is>
       </c>
     </row>
@@ -1462,12 +1462,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_'von_willebrand_disease'}</t>
+          <t>von_willebrand_disease</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': 'von Willebrand Disease'}</t>
+          <t>von Willebrand Disease</t>
         </is>
       </c>
     </row>
@@ -1479,12 +1479,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'value':_'factor_xii_deficiency'}</t>
+          <t>factor_xii_deficiency</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'value': 'Factor XII deficiency'}</t>
+          <t>Factor XII deficiency</t>
         </is>
       </c>
     </row>
@@ -1496,12 +1496,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'value':_'other_(please_specify)'}</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'value': 'Other (please specify)'}</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
@@ -1513,12 +1513,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'value':_'hemophilia_specialist'}</t>
+          <t>hemophilia_specialist</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'value': 'Hemophilia specialist'}</t>
+          <t>Hemophilia specialist</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'value':_'primary_care_physician'}</t>
+          <t>primary_care_physician</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'value': 'Primary care physician'}</t>
+          <t>Primary care physician</t>
         </is>
       </c>
     </row>
@@ -1547,12 +1547,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'value':_'nurse_practitioner'}</t>
+          <t>nurse_practitioner</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'value': 'Nurse practitioner'}</t>
+          <t>Nurse practitioner</t>
         </is>
       </c>
     </row>
@@ -1564,12 +1564,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'value':_'other_(please_specify)'}</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'value': 'Other (please specify)'}</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'value':_'injections'}</t>
+          <t>injections</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'value': 'Injections'}</t>
+          <t>Injections</t>
         </is>
       </c>
     </row>
@@ -1598,12 +1598,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'value':_'infusions'}</t>
+          <t>infusions</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'value': 'Infusions'}</t>
+          <t>Infusions</t>
         </is>
       </c>
     </row>
@@ -1615,12 +1615,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'value':_'oral_medications'}</t>
+          <t>oral_medications</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'value': 'Oral medications'}</t>
+          <t>Oral medications</t>
         </is>
       </c>
     </row>
@@ -1632,12 +1632,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'value':_'other_(please_specify)'}</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'value': 'Other (please specify)'}</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
